--- a/Oekokyst/Stations Nordsjøen.xlsx
+++ b/Oekokyst/Stations Nordsjøen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Oekokyst\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Dashboards\Oekokyst\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1A4D34-C3A3-44F7-A199-355CCBB4B343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004E6BED-C829-40F0-9551-BEF66B336D01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="2055" windowWidth="21600" windowHeight="12645" xr2:uid="{E969CC32-21B0-4D01-9141-475FB54071F0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E969CC32-21B0-4D01-9141-475FB54071F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>Navn</t>
   </si>
   <si>
-    <t>Flekkefjørd ytre</t>
-  </si>
-  <si>
     <t>Jøsenfjord ytre</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>Hidlefjorden</t>
   </si>
   <si>
-    <t>Hjelmedlandsfjorden</t>
-  </si>
-  <si>
     <t>Bjørnafjorden</t>
   </si>
   <si>
@@ -301,6 +295,12 @@
   </si>
   <si>
     <t xml:space="preserve"> m⁻¹</t>
+  </si>
+  <si>
+    <t>Flekkefjørd</t>
+  </si>
+  <si>
+    <t>Hjelmelandsfjorden</t>
   </si>
 </sst>
 </file>
@@ -406,7 +406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -416,9 +416,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,16 +775,16 @@
         <v>22</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -793,7 +792,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -816,8 +815,8 @@
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>25</v>
+      <c r="B3" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -840,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -864,7 +863,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -887,8 +886,8 @@
       <c r="A6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>28</v>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C6" t="s">
         <v>3</v>
@@ -910,8 +909,8 @@
       <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>29</v>
+      <c r="B7" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -933,8 +932,8 @@
       <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>30</v>
+      <c r="B8" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
@@ -956,8 +955,8 @@
       <c r="A9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>31</v>
+      <c r="B9" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
@@ -979,8 +978,8 @@
       <c r="A10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>32</v>
+      <c r="B10" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>3</v>
@@ -1002,8 +1001,8 @@
       <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>33</v>
+      <c r="B11" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
@@ -1022,11 +1021,11 @@
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>34</v>
+      <c r="B12" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>3</v>
@@ -1059,222 +1058,222 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
